--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487912_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487912_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2913</v>
+        <v>3.2148</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5756</v>
+        <v>0.6185</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7158</v>
+        <v>2.5962</v>
       </c>
       <c r="G2" t="n">
-        <v>2.632</v>
+        <v>0.4027</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8719</v>
+        <v>0.5668</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7601</v>
+        <v>-0.1641</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2932</v>
+        <v>0.0232</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2148</v>
+        <v>-0.0944</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0784</v>
+        <v>0.1176</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3388</v>
+        <v>0.3796</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6571</v>
+        <v>0.6612</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6817</v>
+        <v>-0.2817</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.2487</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1218</v>
+        <v>-2.2893</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0319</v>
+        <v>0.6018</v>
       </c>
       <c r="T2" t="n">
-        <v>2.528</v>
+        <v>0.5496</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5039</v>
+        <v>0.0522</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1238</v>
+        <v>3.0427</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1238</v>
+        <v>2.3351</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0221</v>
+        <v>2.9896</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6901</v>
+        <v>-1.1389</v>
       </c>
       <c r="F3" t="n">
-        <v>2.332</v>
+        <v>4.1286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4027</v>
+        <v>2.632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5668</v>
+        <v>1.8719</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1641</v>
+        <v>0.7601</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0232</v>
+        <v>1.2932</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0944</v>
+        <v>1.2148</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1176</v>
+        <v>0.0784</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3796</v>
+        <v>1.3388</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6612</v>
+        <v>0.6571</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2817</v>
+        <v>0.6817</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8325</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2893</v>
+        <v>-3.1218</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4092</v>
+        <v>1.7302</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6212</v>
+        <v>0.8135</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.212</v>
+        <v>0.9167</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0427</v>
+        <v>-0.1238</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3351</v>
+        <v>-0.1238</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6868</v>
+        <v>2.3653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1981</v>
+        <v>-0.1234</v>
       </c>
       <c r="F4" t="n">
         <v>2.4887</v>
@@ -766,10 +766,10 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5219</v>
+        <v>0.2005</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2577</v>
+        <v>-0.0638</v>
       </c>
       <c r="U4" t="n">
         <v>0.2643</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.404</v>
+        <v>0.8722</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9011</v>
+        <v>-0.5796</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3051</v>
+        <v>1.4519</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4363</v>
@@ -844,13 +844,13 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0078</v>
+        <v>0.4761</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4567</v>
+        <v>-0.1352</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4645</v>
+        <v>0.6113</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>D. ROLLINS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3334</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2659</v>
+        <v>-1.1515</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0675</v>
+        <v>0.4936</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2469</v>
+        <v>-0.056</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1471</v>
+        <v>-1.6995</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0997</v>
+        <v>1.6435</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6752</v>
+        <v>-0.1947</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7144</v>
+        <v>-1.4096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>1.2148</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5717</v>
+        <v>0.1387</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4328</v>
+        <v>-0.2899</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1389</v>
+        <v>0.4286</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3721</v>
+        <v>0.2306</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7517</v>
+        <v>0.0838</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ROLLINS</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-1.0611</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3658</v>
+        <v>-0.8057</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4056</v>
+        <v>-0.2554</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.056</v>
+        <v>-2.2469</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6995</v>
+        <v>-1.1471</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6435</v>
+        <v>-1.0997</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1947</v>
+        <v>-0.6752</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4096</v>
+        <v>-0.7144</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2148</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1387</v>
+        <v>-1.5717</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2899</v>
+        <v>-0.4328</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4286</v>
+        <v>-1.1389</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0718</v>
+        <v>0.9776</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1305</v>
+        <v>0.6801</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0587</v>
+        <v>0.2975</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3558</v>
+        <v>-2.9066</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9483</v>
+        <v>-2.734</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4076</v>
+        <v>-0.1727</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9409999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4554</v>
+        <v>-0.0062</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6524</v>
+        <v>-0.4381</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1971</v>
+        <v>0.4319</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7513</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7617</v>
+        <v>-3.2431</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.314</v>
+        <v>-3.8233</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5523</v>
+        <v>0.5802</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.678</v>
+        <v>-4.9166</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4074</v>
+        <v>0.0342</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.2706</v>
+        <v>-4.9508</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.441</v>
+        <v>-3.2101</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8767</v>
+        <v>0.2834</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5643</v>
+        <v>-3.4935</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.237</v>
+        <v>-1.7065</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4693</v>
+        <v>-0.2492</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7063</v>
+        <v>-1.4573</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.538</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3299</v>
+        <v>3.7461</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2076</v>
+        <v>0.2405</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1645</v>
+        <v>0.3025</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0431</v>
+        <v>-0.0619</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2914</v>
+        <v>-2.1051</v>
       </c>
       <c r="W9" t="n">
         <v>-0.7076</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5135</v>
+        <v>-3.5682</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.0893</v>
+        <v>-5.232</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5757</v>
+        <v>1.6638</v>
       </c>
       <c r="G10" t="n">
         <v>-6.687</v>
@@ -1234,13 +1234,13 @@
         <v>3.1218</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8671</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3948</v>
+        <v>0.4625</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4723</v>
+        <v>-0.3842</v>
       </c>
       <c r="V10" t="n">
         <v>1.1675</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8505</v>
+        <v>-3.8792</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4307</v>
+        <v>-5.314</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5802</v>
+        <v>1.4348</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9166</v>
+        <v>-3.678</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0342</v>
+        <v>-0.4074</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.9508</v>
+        <v>-3.2706</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2101</v>
+        <v>-2.441</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2834</v>
+        <v>-0.8767</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.4935</v>
+        <v>-1.5643</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7065</v>
+        <v>-1.237</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2492</v>
+        <v>0.4693</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4573</v>
+        <v>-1.7063</v>
       </c>
       <c r="P11" t="n">
-        <v>3.538</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7461</v>
+        <v>3.3299</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3668</v>
+        <v>1.0901</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3049</v>
+        <v>1.1645</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0619</v>
+        <v>-0.0743</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1051</v>
+        <v>-1.2914</v>
       </c>
       <c r="W11" t="n">
         <v>-0.7076</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3975</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6017</v>
+        <v>-5.4318</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.5905</v>
+        <v>-5.6261</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0112</v>
+        <v>0.1943</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8966</v>
@@ -1390,13 +1390,13 @@
         <v>3.3299</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6864</v>
+        <v>0.4835</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3948</v>
+        <v>0.5696</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2916</v>
+        <v>-0.0861</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9376</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.3058</v>
+        <v>-11.3059</v>
       </c>
       <c r="E13" t="n">
         <v>-25.91</v>
       </c>
       <c r="F13" t="n">
-        <v>14.6041</v>
+        <v>14.604</v>
       </c>
       <c r="G13" t="n">
         <v>-16.4508</v>
@@ -1471,13 +1471,13 @@
         <v>6.103000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.989000000000001</v>
+        <v>3.989</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1143</v>
+        <v>2.1142</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.999</v>
+        <v>-1.999000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>2.4236</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.512</v>
+        <v>3.7658</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9408</v>
+        <v>-0.3874</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5713</v>
+        <v>4.1532</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1843</v>
+        <v>4.4635</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4969</v>
+        <v>1.3048</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6812</v>
+        <v>3.1587</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0129</v>
+        <v>2.7941</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9173</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9301</v>
+        <v>1.9055</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1714</v>
+        <v>1.6694</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4203</v>
+        <v>0.4162</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7511</v>
+        <v>1.2532</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2487</v>
+        <v>3.1218</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.8246</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.199</v>
+        <v>-0.1866</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5565</v>
+        <v>-0.638</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8751</v>
+        <v>1.1675</v>
       </c>
       <c r="W14" t="n">
         <v>1.1675</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8499</v>
+        <v>3.4739</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2446</v>
+        <v>0.7265</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0945</v>
+        <v>2.7474</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4635</v>
+        <v>2.1843</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3048</v>
+        <v>-1.4969</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1587</v>
+        <v>3.6812</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7941</v>
+        <v>1.0129</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8885999999999999</v>
+        <v>-1.9173</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9055</v>
+        <v>2.9301</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6694</v>
+        <v>1.1714</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4162</v>
+        <v>0.4203</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2532</v>
+        <v>0.7511</v>
       </c>
       <c r="P15" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-4.1624</v>
-      </c>
       <c r="R15" t="n">
-        <v>3.1218</v>
+        <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7406</v>
+        <v>-0.7937</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0439</v>
+        <v>-0.4133</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6967</v>
+        <v>-0.3803</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1675</v>
+        <v>1.8751</v>
       </c>
       <c r="W15" t="n">
         <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4322</v>
+        <v>2.2091</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3823</v>
+        <v>-0.0463</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0499</v>
+        <v>2.2554</v>
       </c>
       <c r="G16" t="n">
         <v>2.3075</v>
@@ -1702,13 +1702,13 @@
         <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3321</v>
+        <v>-0.5552</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4501</v>
+        <v>0.0215</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7822</v>
+        <v>-0.5767</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5838</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.69</v>
+        <v>0.7955</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7805</v>
+        <v>-3.199</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4705</v>
+        <v>3.9945</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0248</v>
+        <v>0.8498</v>
       </c>
       <c r="H17" t="n">
-        <v>1.548</v>
+        <v>-1.8444</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4768</v>
+        <v>2.6942</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5309</v>
+        <v>-0.6564</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1277</v>
+        <v>-2.028</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5968</v>
+        <v>1.3716</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4939</v>
+        <v>1.5062</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4203</v>
+        <v>0.1836</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0736</v>
+        <v>1.3226</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0812</v>
+        <v>2.7055</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0596</v>
+        <v>-0.6787</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0033</v>
+        <v>-0.4615</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0629</v>
+        <v>-0.2172</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5915</v>
+        <v>0.5949</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.5205</v>
+        <v>-1.9948</v>
       </c>
       <c r="F18" t="n">
-        <v>4.112</v>
+        <v>2.5897</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8498</v>
+        <v>2.0248</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8444</v>
+        <v>1.548</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6942</v>
+        <v>0.4768</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6564</v>
+        <v>0.5309</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.028</v>
+        <v>1.1277</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3716</v>
+        <v>-0.5968</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5062</v>
+        <v>1.4939</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1836</v>
+        <v>0.4203</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3226</v>
+        <v>1.0736</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7055</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8827</v>
+        <v>-0.0355</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7829</v>
+        <v>-0.2176</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0998</v>
+        <v>0.1821</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4493</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3653</v>
+        <v>-3.9922</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08400000000000001</v>
+        <v>4.5392</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7943</v>
+        <v>0.5707</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6737</v>
+        <v>0.6654</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4679</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.222</v>
+        <v>-1.4661</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.045</v>
+        <v>-0.2243</v>
       </c>
       <c r="L19" t="n">
-        <v>0.823</v>
+        <v>-1.2418</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0163</v>
+        <v>2.0368</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3713</v>
+        <v>0.8897</v>
       </c>
       <c r="O19" t="n">
-        <v>0.645</v>
+        <v>1.1471</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>3.7461</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0327</v>
+        <v>-1.5857</v>
       </c>
       <c r="T19" t="n">
-        <v>1.295</v>
+        <v>-0.5719</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2622</v>
+        <v>-1.0138</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.0427</v>
+        <v>0.9376</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3351</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. PASCUAL BLANCO</t>
+          <t>D. MIRANDA PASCUAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3053</v>
+        <v>0.3347</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3053</v>
+        <v>0.3347</v>
       </c>
       <c r="G20" t="n">
         <v>0.2857</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MIRANDA PASCUAL</t>
+          <t>R. PASCUAL BLANCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3053</v>
+        <v>0.3347</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3053</v>
+        <v>0.3347</v>
       </c>
       <c r="G21" t="n">
         <v>0.2857</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1565</v>
+        <v>0.0195</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2066</v>
+        <v>-5.0046</v>
       </c>
       <c r="F22" t="n">
-        <v>4.363</v>
+        <v>5.024</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5707</v>
+        <v>2.6844</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6654</v>
+        <v>1.9512</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.7331</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4661</v>
+        <v>0.9334</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2243</v>
+        <v>1.2044</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2418</v>
+        <v>-0.2711</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0368</v>
+        <v>1.751</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8897</v>
+        <v>0.7468</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1471</v>
+        <v>1.0042</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6244</v>
+        <v>-3.1218</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1218</v>
+        <v>-6.2435</v>
       </c>
       <c r="R22" t="n">
-        <v>3.7461</v>
+        <v>3.1218</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9761</v>
+        <v>-1.5421</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7862</v>
+        <v>-0.5081</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1899</v>
+        <v>-1.034</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9376</v>
+        <v>1.999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.23</v>
+        <v>1.1852</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.986</v>
+        <v>-0.7691</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5403</v>
+        <v>-0.7062</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5543</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6844</v>
+        <v>0.7943</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9512</v>
+        <v>-0.6737</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7331</v>
+        <v>1.4679</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9334</v>
+        <v>-0.222</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2044</v>
+        <v>-1.045</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2711</v>
+        <v>0.823</v>
       </c>
       <c r="M23" t="n">
-        <v>1.751</v>
+        <v>1.0163</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7468</v>
+        <v>0.3713</v>
       </c>
       <c r="O23" t="n">
-        <v>1.0042</v>
+        <v>0.645</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.1218</v>
+        <v>1.6649</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6.2435</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1218</v>
+        <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.5476</v>
+        <v>-0.1856</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0439</v>
+        <v>0.2234</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5037</v>
+        <v>-0.409</v>
       </c>
       <c r="V23" t="n">
-        <v>1.999</v>
+        <v>-3.0427</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8137</v>
+        <v>-0.7076</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1852</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.306</v>
+        <v>11.3059</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.6041</v>
+        <v>-14.604</v>
       </c>
       <c r="F24" t="n">
-        <v>25.9101</v>
+        <v>25.91</v>
       </c>
       <c r="G24" t="n">
         <v>16.4507</v>
@@ -2299,13 +2299,13 @@
         <v>14.0831</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8996</v>
+        <v>3.899599999999999</v>
       </c>
       <c r="K24" t="n">
         <v>-1.5909</v>
       </c>
       <c r="L24" t="n">
-        <v>5.4904</v>
+        <v>5.490399999999999</v>
       </c>
       <c r="M24" t="n">
         <v>12.5511</v>
@@ -2326,13 +2326,13 @@
         <v>19.7712</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.1031</v>
+        <v>-6.1033</v>
       </c>
       <c r="T24" t="n">
         <v>-2.114100000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.9889</v>
+        <v>-3.9891</v>
       </c>
       <c r="V24" t="n">
         <v>1.998900000000001</v>
